--- a/interview_forms/018_full_stack_developer_interview_form--interview_forms.xlsx
+++ b/interview_forms/018_full_stack_developer_interview_form--interview_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1134,12 +1134,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'web_development',_'value':_'web-development'}</t>
+          <t>web_development</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Web development', 'value': 'web-development'}</t>
+          <t>Web development</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'backend',_'value':_'backend'}</t>
+          <t>backend</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Backend', 'value': 'backend'}</t>
+          <t>Backend</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'frontend',_'value':_'frontend'}</t>
+          <t>frontend</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Frontend', 'value': 'frontend'}</t>
+          <t>Frontend</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'database',_'value':_'database'}</t>
+          <t>database</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Database', 'value': 'database'}</t>
+          <t>Database</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'cloud',_'value':_'cloud'}</t>
+          <t>cloud</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Cloud', 'value': 'cloud'}</t>
+          <t>Cloud</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'devops',_'value':_'devops'}</t>
+          <t>devops</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'DevOps', 'value': 'devops'}</t>
+          <t>DevOps</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'testing',_'value':_'testing'}</t>
+          <t>testing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Testing', 'value': 'testing'}</t>
+          <t>Testing</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'devops',_'value':_'devops'}</t>
+          <t>machine_learning</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'DevOps', 'value': 'devops'}</t>
+          <t>Machine Learning</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'machine_learning',_'value':_'machine-learning'}</t>
+          <t>data_science</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Machine Learning', 'value': 'machine-learning'}</t>
+          <t>Data Science</t>
         </is>
       </c>
     </row>
@@ -1320,29 +1320,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'data_science',_'value':_'data-science'}</t>
+          <t>full-stack</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Data Science', 'value': 'data-science'}</t>
+          <t>Full-stack</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>technical_stack_choices</t>
+          <t>technical_skills_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'full-stack',_'value':_'full-stack'}</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Full-stack', 'value': 'full-stack'}</t>
+          <t>HTML</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'html',_'value':_'html'}</t>
+          <t>css</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'HTML', 'value': 'html'}</t>
+          <t>CSS</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'css',_'value':_'css'}</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'CSS', 'value': 'css'}</t>
+          <t>JavaScript</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'javascript',_'value':_'javascript'}</t>
+          <t>java</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'JavaScript', 'value': 'javascript'}</t>
+          <t>Java</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'java',_'value':_'java'}</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Java', 'value': 'java'}</t>
+          <t>Python</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'python',_'value':_'python'}</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Python', 'value': 'python'}</t>
+          <t>SQL</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'sql',_'value':_'sql'}</t>
+          <t>c++</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'SQL', 'value': 'sql'}</t>
+          <t>C++</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'c++',_'value':_'cplusplus'}</t>
+          <t>c#</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'C++', 'value': 'cplusplus'}</t>
+          <t>C#</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'c#',_'value':_'csharp'}</t>
+          <t>react</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'C#', 'value': 'csharp'}</t>
+          <t>React</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'react',_'value':_'react'}</t>
+          <t>angular</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'React', 'value': 'react'}</t>
+          <t>Angular</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'angular',_'value':_'angular'}</t>
+          <t>vue</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Angular', 'value': 'angular'}</t>
+          <t>Vue</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'vue',_'value':_'vue'}</t>
+          <t>django</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Vue', 'value': 'vue'}</t>
+          <t>Django</t>
         </is>
       </c>
     </row>
@@ -1541,29 +1541,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'django',_'value':_'django'}</t>
+          <t>node.js</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Django', 'value': 'django'}</t>
+          <t>Node.js</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>technical_skills_choices</t>
+          <t>interview_preferences_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'node.js',_'value':_'nodejs'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Node.js', 'value': 'nodejs'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'phone',_'value':_'phone'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Phone', 'value': 'phone'}</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'video',_'value':_'video'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Video', 'value': 'video'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -1609,29 +1609,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'in-person',_'value':_'in-person'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'In-person', 'value': 'in-person'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>interview_preferences_choices</t>
+          <t>interview_preferences_input_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'online',_'value':_'online'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Online', 'value': 'online'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'phone',_'value':_'phone'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Phone', 'value': 'phone'}</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'video',_'value':_'video'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Video', 'value': 'video'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -1677,29 +1677,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'in-person',_'value':_'in-person'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'In-person', 'value': 'in-person'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>interview_preferences_input_choices</t>
+          <t>technical_skills_input_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'online',_'value':_'online'}</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Online', 'value': 'online'}</t>
+          <t>HTML</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'html',_'value':_'html'}</t>
+          <t>css</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'HTML', 'value': 'html'}</t>
+          <t>CSS</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'css',_'value':_'css'}</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'CSS', 'value': 'css'}</t>
+          <t>JavaScript</t>
         </is>
       </c>
     </row>
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'javascript',_'value':_'javascript'}</t>
+          <t>java</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'JavaScript', 'value': 'javascript'}</t>
+          <t>Java</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'java',_'value':_'java'}</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Java', 'value': 'java'}</t>
+          <t>Python</t>
         </is>
       </c>
     </row>
@@ -1779,12 +1779,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'python',_'value':_'python'}</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Python', 'value': 'python'}</t>
+          <t>SQL</t>
         </is>
       </c>
     </row>
@@ -1796,12 +1796,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'sql',_'value':_'sql'}</t>
+          <t>c++</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'SQL', 'value': 'sql'}</t>
+          <t>C++</t>
         </is>
       </c>
     </row>
@@ -1813,12 +1813,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'c++',_'value':_'cplusplus'}</t>
+          <t>c#</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'C++', 'value': 'cplusplus'}</t>
+          <t>C#</t>
         </is>
       </c>
     </row>
@@ -1830,12 +1830,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'c#',_'value':_'csharp'}</t>
+          <t>react</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'C#', 'value': 'csharp'}</t>
+          <t>React</t>
         </is>
       </c>
     </row>
@@ -1847,12 +1847,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'react',_'value':_'react'}</t>
+          <t>angular</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'React', 'value': 'react'}</t>
+          <t>Angular</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'angular',_'value':_'angular'}</t>
+          <t>vue</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Angular', 'value': 'angular'}</t>
+          <t>Vue</t>
         </is>
       </c>
     </row>
@@ -1881,12 +1881,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'vue',_'value':_'vue'}</t>
+          <t>django</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Vue', 'value': 'vue'}</t>
+          <t>Django</t>
         </is>
       </c>
     </row>
@@ -1898,29 +1898,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'django',_'value':_'django'}</t>
+          <t>node.js</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Django', 'value': 'django'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>technical_skills_input_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>{'label':_'node.js',_'value':_'nodejs'}</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>{'label': 'Node.js', 'value': 'nodejs'}</t>
+          <t>Node.js</t>
         </is>
       </c>
     </row>
